--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-prescription-extension.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-prescription-extension.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Fr Prescription</t>
+    <t>Extension - Fr Prescription</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Instructions de prescription associées à l'administration du produit de santé.</t>
+    <t>Extension permettant d’indiquer les instructions de prescription associées à l'administration du produit de santé.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -938,10 +938,10 @@
 </t>
   </si>
   <si>
-    <t>Fr Repeat Number</t>
-  </si>
-  <si>
-    <t>Numéro d'occurrence de l'acte ou de l'observation (équivalent CDA repeatNumber)</t>
+    <t>Extension - Fr Repeat Number</t>
+  </si>
+  <si>
+    <t>Extension permettant d'indiquer le numéro d'occurrence de l'acte ou de l'observation.</t>
   </si>
   <si>
     <t>Extension.extension:prescripteur</t>
